--- a/docs/Prime_Capital_Bank_Analytics.xlsx
+++ b/docs/Prime_Capital_Bank_Analytics.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="165" formatCode="R#,##0"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="25">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -149,8 +149,31 @@
       <color rgb="009C0006"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="00C9A84C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="001C2B3A"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001C2B3A"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="13">
     <fill>
       <patternFill/>
     </fill>
@@ -202,8 +225,18 @@
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000A1628"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000F2040"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -269,11 +302,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00DDE5F0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00DDE5F0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00DDE5F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00DDE5F0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -440,6 +487,66 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="23" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="23" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="21" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="23" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="23" fillId="8" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -845,7 +952,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="44" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="60" t="inlineStr">
         <is>
           <t>PRIME CAPITAL BANK — DATA INTELLIGENCE PLATFORM</t>
         </is>
@@ -865,21 +972,25 @@
           <t>Total Assets</t>
         </is>
       </c>
+      <c r="B4" s="53" t="n"/>
       <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Total Loans</t>
         </is>
       </c>
+      <c r="D4" s="53" t="n"/>
       <c r="E4" s="3" t="inlineStr">
         <is>
           <t>NPL Ratio</t>
         </is>
       </c>
+      <c r="F4" s="53" t="n"/>
       <c r="G4" s="3" t="inlineStr">
         <is>
           <t>CET1 Capital Ratio</t>
         </is>
       </c>
+      <c r="H4" s="53" t="n"/>
     </row>
     <row r="5" ht="38" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
@@ -887,21 +998,25 @@
           <t>R847.3B</t>
         </is>
       </c>
+      <c r="B5" s="53" t="n"/>
       <c r="C5" s="4" t="inlineStr">
         <is>
           <t>R312.6B</t>
         </is>
       </c>
+      <c r="D5" s="53" t="n"/>
       <c r="E5" s="5" t="inlineStr">
         <is>
           <t>2.8%</t>
         </is>
       </c>
+      <c r="F5" s="53" t="n"/>
       <c r="G5" s="4" t="inlineStr">
         <is>
           <t>14.2%</t>
         </is>
       </c>
+      <c r="H5" s="53" t="n"/>
     </row>
     <row r="6" ht="6" customHeight="1"/>
     <row r="7" ht="20" customHeight="1">
@@ -910,21 +1025,25 @@
           <t>Return on Equity</t>
         </is>
       </c>
+      <c r="B7" s="53" t="n"/>
       <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Return on Assets</t>
         </is>
       </c>
+      <c r="D7" s="53" t="n"/>
       <c r="E7" s="3" t="inlineStr">
         <is>
           <t>Net Interest Margin</t>
         </is>
       </c>
+      <c r="F7" s="53" t="n"/>
       <c r="G7" s="3" t="inlineStr">
         <is>
           <t>Cost-to-Income</t>
         </is>
       </c>
+      <c r="H7" s="53" t="n"/>
     </row>
     <row r="8" ht="38" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
@@ -932,22 +1051,27 @@
           <t>18.4%</t>
         </is>
       </c>
+      <c r="B8" s="53" t="n"/>
       <c r="C8" s="4" t="inlineStr">
         <is>
           <t>1.7%</t>
         </is>
       </c>
+      <c r="D8" s="53" t="n"/>
       <c r="E8" s="4" t="inlineStr">
         <is>
           <t>4.2%</t>
         </is>
       </c>
+      <c r="F8" s="53" t="n"/>
       <c r="G8" s="5" t="inlineStr">
         <is>
           <t>52.1%</t>
         </is>
       </c>
-    </row>
+      <c r="H8" s="53" t="n"/>
+    </row>
+    <row r="9"/>
     <row r="10" ht="8" customHeight="1"/>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -968,7 +1092,7 @@
     </row>
     <row r="12" ht="8" customHeight="1"/>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="61" t="inlineStr">
         <is>
           <t>PIPELINE ARCHITECTURE SUMMARY</t>
         </is>
@@ -1017,42 +1141,42 @@
       </c>
     </row>
     <row r="15" ht="16" customHeight="1">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="62" t="inlineStr">
         <is>
           <t>Bronze</t>
         </is>
       </c>
-      <c r="B15" s="11" t="inlineStr">
+      <c r="B15" s="62" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="C15" s="11" t="inlineStr">
+      <c r="C15" s="62" t="inlineStr">
         <is>
           <t>830,000+</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="63" t="inlineStr">
         <is>
           <t>Raw ingestion — synthetic Delta Lake data</t>
         </is>
       </c>
-      <c r="E15" s="11" t="inlineStr">
+      <c r="E15" s="62" t="inlineStr">
         <is>
           <t>PySpark + Delta Lake</t>
         </is>
       </c>
-      <c r="F15" s="11" t="inlineStr">
+      <c r="F15" s="62" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G15" s="62" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="H15" s="13" t="inlineStr">
+      <c r="H15" s="64" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
@@ -1101,42 +1225,42 @@
       </c>
     </row>
     <row r="17" ht="16" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="62" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="B17" s="11" t="inlineStr">
+      <c r="B17" s="62" t="inlineStr">
         <is>
           <t>4+</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="62" t="inlineStr">
         <is>
           <t>Star schema</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="63" t="inlineStr">
         <is>
           <t>Dim/Fact MERGE + Z-order + OPTIMIZE</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="62" t="inlineStr">
         <is>
           <t>Delta Lake + DeltaTable</t>
         </is>
       </c>
-      <c r="F17" s="11" t="inlineStr">
+      <c r="F17" s="62" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="G17" s="62" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="H17" s="13" t="inlineStr">
+      <c r="H17" s="64" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
@@ -1185,42 +1309,42 @@
       </c>
     </row>
     <row r="19" ht="16" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="62" t="inlineStr">
         <is>
           <t>Regulatory</t>
         </is>
       </c>
-      <c r="B19" s="11" t="inlineStr">
+      <c r="B19" s="62" t="inlineStr">
         <is>
           <t>5 reports</t>
         </is>
       </c>
-      <c r="C19" s="11" t="inlineStr">
+      <c r="C19" s="62" t="inlineStr">
         <is>
           <t>SARB/Basel</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="63" t="inlineStr">
         <is>
           <t>Capital / LCR / NSFR / SAR reporting</t>
         </is>
       </c>
-      <c r="E19" s="11" t="inlineStr">
+      <c r="E19" s="62" t="inlineStr">
         <is>
           <t>PySpark + Delta</t>
         </is>
       </c>
-      <c r="F19" s="11" t="inlineStr">
+      <c r="F19" s="62" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="G19" s="62" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="H19" s="13" t="inlineStr">
+      <c r="H19" s="64" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
@@ -1274,71 +1398,71 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="60" t="inlineStr">
         <is>
           <t>PRIME CAPITAL BANK — LOAN PORTFOLIO ANALYSIS  |  FY 2025</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="65" t="inlineStr">
         <is>
           <t>Loan Type</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="65" t="inlineStr">
         <is>
           <t>Book Value (Rm)</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr">
+      <c r="C2" s="65" t="inlineStr">
         <is>
           <t>NPL Rate (%)</t>
         </is>
       </c>
-      <c r="D2" s="18" t="inlineStr">
+      <c r="D2" s="65" t="inlineStr">
         <is>
           <t>ECL Provision (Rm)</t>
         </is>
       </c>
-      <c r="E2" s="18" t="inlineStr">
+      <c r="E2" s="65" t="inlineStr">
         <is>
           <t>Coverage Ratio (%)</t>
         </is>
       </c>
-      <c r="F2" s="18" t="inlineStr">
+      <c r="F2" s="65" t="inlineStr">
         <is>
           <t>Avg Interest Rate (%)</t>
         </is>
       </c>
-      <c r="G2" s="18" t="inlineStr">
+      <c r="G2" s="65" t="inlineStr">
         <is>
           <t>LGD (%)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="19" t="inlineStr">
+      <c r="A3" s="66" t="inlineStr">
         <is>
           <t>Home Loans</t>
         </is>
       </c>
-      <c r="B3" s="20" t="n">
+      <c r="B3" s="67" t="n">
         <v>124800</v>
       </c>
-      <c r="C3" s="21" t="n">
+      <c r="C3" s="68" t="n">
         <v>0.012</v>
       </c>
-      <c r="D3" s="20" t="n">
+      <c r="D3" s="67" t="n">
         <v>2994</v>
       </c>
-      <c r="E3" s="21" t="n">
+      <c r="E3" s="68" t="n">
         <v>0.24</v>
       </c>
-      <c r="F3" s="21" t="n">
+      <c r="F3" s="68" t="n">
         <v>0.098</v>
       </c>
-      <c r="G3" s="21" t="n">
+      <c r="G3" s="68" t="n">
         <v>0.18</v>
       </c>
     </row>
@@ -1368,27 +1492,27 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="19" t="inlineStr">
+      <c r="A5" s="66" t="inlineStr">
         <is>
           <t>Vehicle Finance</t>
         </is>
       </c>
-      <c r="B5" s="20" t="n">
+      <c r="B5" s="67" t="n">
         <v>67400</v>
       </c>
-      <c r="C5" s="21" t="n">
+      <c r="C5" s="68" t="n">
         <v>0.029</v>
       </c>
-      <c r="D5" s="20" t="n">
+      <c r="D5" s="67" t="n">
         <v>3893</v>
       </c>
-      <c r="E5" s="21" t="n">
+      <c r="E5" s="68" t="n">
         <v>0.5659999999999999</v>
       </c>
-      <c r="F5" s="21" t="n">
+      <c r="F5" s="68" t="n">
         <v>0.112</v>
       </c>
-      <c r="G5" s="21" t="n">
+      <c r="G5" s="68" t="n">
         <v>0.28</v>
       </c>
     </row>
@@ -1418,36 +1542,37 @@
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="69" t="inlineStr">
         <is>
           <t>TOTAL / AVERAGE</t>
         </is>
       </c>
-      <c r="B7" s="26">
+      <c r="B7" s="70">
         <f>SUM(B3:B6)</f>
         <v/>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="71">
         <f>SUMPRODUCT(B3:B6,C3:C6)/SUM(B3:B6)</f>
         <v/>
       </c>
-      <c r="D7" s="26">
+      <c r="D7" s="70">
         <f>SUM(D3:D6)</f>
         <v/>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="71">
         <f>SUMPRODUCT(B3:B6,E3:E6)/SUM(B3:B6)</f>
         <v/>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="71">
         <f>SUMPRODUCT(B3:B6,F3:F6)/SUM(B3:B6)</f>
         <v/>
       </c>
-      <c r="G7" s="27">
+      <c r="G7" s="71">
         <f>SUMPRODUCT(B3:B6,G3:G6)/SUM(B3:B6)</f>
         <v/>
       </c>
     </row>
+    <row r="8"/>
     <row r="9" ht="14" customHeight="1">
       <c r="A9" s="28" t="inlineStr">
         <is>
@@ -1496,72 +1621,72 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="60" t="inlineStr">
         <is>
           <t>PRIME CAPITAL BANK — FRAUD INTELLIGENCE DASHBOARD  |  FY 2025</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="65" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="65" t="inlineStr">
         <is>
           <t>Card Transactions</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr">
+      <c r="C2" s="65" t="inlineStr">
         <is>
           <t>Fraud Alerts</t>
         </is>
       </c>
-      <c r="D2" s="18" t="inlineStr">
+      <c r="D2" s="65" t="inlineStr">
         <is>
           <t>Fraud Rate (%)</t>
         </is>
       </c>
-      <c r="E2" s="18" t="inlineStr">
+      <c r="E2" s="65" t="inlineStr">
         <is>
           <t>False Positive Rate (%)</t>
         </is>
       </c>
-      <c r="F2" s="18" t="inlineStr">
+      <c r="F2" s="65" t="inlineStr">
         <is>
           <t>Avg Fraud Amount (R)</t>
         </is>
       </c>
-      <c r="G2" s="18" t="inlineStr">
+      <c r="G2" s="65" t="inlineStr">
         <is>
           <t>Total Fraud Loss (R)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="64" t="inlineStr">
         <is>
           <t>Jan 2025</t>
         </is>
       </c>
-      <c r="B3" s="20" t="n">
+      <c r="B3" s="67" t="n">
         <v>16200</v>
       </c>
-      <c r="C3" s="20">
+      <c r="C3" s="67">
         <f>ROUND(B3*D3,0)</f>
         <v/>
       </c>
-      <c r="D3" s="30" t="n">
+      <c r="D3" s="72" t="n">
         <v>0.0009</v>
       </c>
-      <c r="E3" s="21" t="n">
+      <c r="E3" s="68" t="n">
         <v>0.041</v>
       </c>
-      <c r="F3" s="31" t="n">
+      <c r="F3" s="73" t="n">
         <v>4850</v>
       </c>
-      <c r="G3" s="31">
+      <c r="G3" s="73">
         <f>C3*F3</f>
         <v/>
       </c>
@@ -1594,28 +1719,28 @@
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="64" t="inlineStr">
         <is>
           <t>Mar 2025</t>
         </is>
       </c>
-      <c r="B5" s="20" t="n">
+      <c r="B5" s="67" t="n">
         <v>17100</v>
       </c>
-      <c r="C5" s="20">
+      <c r="C5" s="67">
         <f>ROUND(B5*D5,0)</f>
         <v/>
       </c>
-      <c r="D5" s="30" t="n">
+      <c r="D5" s="72" t="n">
         <v>0.0008</v>
       </c>
-      <c r="E5" s="21" t="n">
+      <c r="E5" s="68" t="n">
         <v>0.042</v>
       </c>
-      <c r="F5" s="31" t="n">
+      <c r="F5" s="73" t="n">
         <v>4600</v>
       </c>
-      <c r="G5" s="31">
+      <c r="G5" s="73">
         <f>C5*F5</f>
         <v/>
       </c>
@@ -1648,28 +1773,28 @@
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="64" t="inlineStr">
         <is>
           <t>May 2025</t>
         </is>
       </c>
-      <c r="B7" s="20" t="n">
+      <c r="B7" s="67" t="n">
         <v>17400</v>
       </c>
-      <c r="C7" s="20">
+      <c r="C7" s="67">
         <f>ROUND(B7*D7,0)</f>
         <v/>
       </c>
-      <c r="D7" s="30" t="n">
+      <c r="D7" s="72" t="n">
         <v>0.001</v>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="68" t="n">
         <v>0.039</v>
       </c>
-      <c r="F7" s="31" t="n">
+      <c r="F7" s="73" t="n">
         <v>5100</v>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="73">
         <f>C7*F7</f>
         <v/>
       </c>
@@ -1702,28 +1827,28 @@
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="64" t="inlineStr">
         <is>
           <t>Jul 2025</t>
         </is>
       </c>
-      <c r="B9" s="20" t="n">
+      <c r="B9" s="67" t="n">
         <v>17800</v>
       </c>
-      <c r="C9" s="20">
+      <c r="C9" s="67">
         <f>ROUND(B9*D9,0)</f>
         <v/>
       </c>
-      <c r="D9" s="30" t="n">
+      <c r="D9" s="72" t="n">
         <v>0.0011</v>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="68" t="n">
         <v>0.043</v>
       </c>
-      <c r="F9" s="31" t="n">
+      <c r="F9" s="73" t="n">
         <v>5500</v>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="73">
         <f>C9*F9</f>
         <v/>
       </c>
@@ -1756,28 +1881,28 @@
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="64" t="inlineStr">
         <is>
           <t>Sep 2025</t>
         </is>
       </c>
-      <c r="B11" s="20" t="n">
+      <c r="B11" s="67" t="n">
         <v>17200</v>
       </c>
-      <c r="C11" s="20">
+      <c r="C11" s="67">
         <f>ROUND(B11*D11,0)</f>
         <v/>
       </c>
-      <c r="D11" s="30" t="n">
+      <c r="D11" s="72" t="n">
         <v>0.0014</v>
       </c>
-      <c r="E11" s="21" t="n">
+      <c r="E11" s="68" t="n">
         <v>0.048</v>
       </c>
-      <c r="F11" s="31" t="n">
+      <c r="F11" s="73" t="n">
         <v>6800</v>
       </c>
-      <c r="G11" s="31">
+      <c r="G11" s="73">
         <f>C11*F11</f>
         <v/>
       </c>
@@ -1810,28 +1935,28 @@
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="64" t="inlineStr">
         <is>
           <t>Nov 2025</t>
         </is>
       </c>
-      <c r="B13" s="20" t="n">
+      <c r="B13" s="67" t="n">
         <v>19800</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="67">
         <f>ROUND(B13*D13,0)</f>
         <v/>
       </c>
-      <c r="D13" s="30" t="n">
+      <c r="D13" s="72" t="n">
         <v>0.0013</v>
       </c>
-      <c r="E13" s="21" t="n">
+      <c r="E13" s="68" t="n">
         <v>0.047</v>
       </c>
-      <c r="F13" s="31" t="n">
+      <c r="F13" s="73" t="n">
         <v>6400</v>
       </c>
-      <c r="G13" s="31">
+      <c r="G13" s="73">
         <f>C13*F13</f>
         <v/>
       </c>
@@ -1864,32 +1989,32 @@
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="35" t="inlineStr">
+      <c r="A15" s="74" t="inlineStr">
         <is>
           <t>TOTAL / AVG</t>
         </is>
       </c>
-      <c r="B15" s="26">
+      <c r="B15" s="70">
         <f>SUM(B3:B14)</f>
         <v/>
       </c>
-      <c r="C15" s="26">
+      <c r="C15" s="70">
         <f>SUM(C3:C14)</f>
         <v/>
       </c>
-      <c r="D15" s="36">
+      <c r="D15" s="75">
         <f>AVERAGE(D3:D14)</f>
         <v/>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="71">
         <f>AVERAGE(E3:E14)</f>
         <v/>
       </c>
-      <c r="F15" s="37">
+      <c r="F15" s="76">
         <f>AVERAGE(F3:F14)</f>
         <v/>
       </c>
-      <c r="G15" s="37">
+      <c r="G15" s="76">
         <f>SUM(G3:G14)</f>
         <v/>
       </c>
@@ -1919,34 +2044,34 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="60" t="inlineStr">
         <is>
           <t>PRIME CAPITAL BANK — REGULATORY CAPITAL &amp; LIQUIDITY  |  Basel III / SARB</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="65" t="inlineStr">
         <is>
           <t>Ratio</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="65" t="inlineStr">
         <is>
           <t>Actual (%)</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr">
+      <c r="C2" s="65" t="inlineStr">
         <is>
           <t>Min Requirement (%)</t>
         </is>
       </c>
-      <c r="D2" s="18" t="inlineStr">
+      <c r="D2" s="65" t="inlineStr">
         <is>
           <t>Buffer (%)</t>
         </is>
       </c>
-      <c r="E2" s="18" t="inlineStr">
+      <c r="E2" s="65" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
@@ -1958,6 +2083,10 @@
           <t>CAPITAL ADEQUACY</t>
         </is>
       </c>
+      <c r="B3" s="52" t="n"/>
+      <c r="C3" s="52" t="n"/>
+      <c r="D3" s="52" t="n"/>
+      <c r="E3" s="53" t="n"/>
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="38" t="inlineStr">
@@ -1987,13 +2116,13 @@
           <t>Tier 1 Capital Ratio</t>
         </is>
       </c>
-      <c r="B5" s="41" t="n">
+      <c r="B5" s="77" t="n">
         <v>0.158</v>
       </c>
-      <c r="C5" s="41" t="n">
+      <c r="C5" s="77" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="D5" s="41">
+      <c r="D5" s="77">
         <f>B5-C5</f>
         <v/>
       </c>
@@ -2031,6 +2160,10 @@
           <t>LIQUIDITY REQUIREMENTS</t>
         </is>
       </c>
+      <c r="B7" s="52" t="n"/>
+      <c r="C7" s="52" t="n"/>
+      <c r="D7" s="52" t="n"/>
+      <c r="E7" s="53" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="38" t="inlineStr">
@@ -2060,13 +2193,13 @@
           <t>Net Stable Funding Ratio (NSFR)</t>
         </is>
       </c>
-      <c r="B9" s="41" t="n">
+      <c r="B9" s="77" t="n">
         <v>1.126</v>
       </c>
-      <c r="C9" s="41" t="n">
+      <c r="C9" s="77" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="41">
+      <c r="D9" s="77">
         <f>B9-C9</f>
         <v/>
       </c>
@@ -2098,6 +2231,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="14" customHeight="1">
       <c r="A12" s="28" t="inlineStr">
         <is>
@@ -2136,82 +2270,82 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
-      <c r="A1" s="17" t="inlineStr">
+      <c r="A1" s="60" t="inlineStr">
         <is>
           <t>PRIME CAPITAL BANK — MACHINE LEARNING MODEL REGISTRY  |  FY 2025</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="18" t="inlineStr">
+      <c r="A2" s="65" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="B2" s="18" t="inlineStr">
+      <c r="B2" s="65" t="inlineStr">
         <is>
           <t>Algorithm</t>
         </is>
       </c>
-      <c r="C2" s="18" t="inlineStr">
+      <c r="C2" s="65" t="inlineStr">
         <is>
           <t>Training Records</t>
         </is>
       </c>
-      <c r="D2" s="18" t="inlineStr">
+      <c r="D2" s="65" t="inlineStr">
         <is>
           <t>AUC-ROC</t>
         </is>
       </c>
-      <c r="E2" s="18" t="inlineStr">
+      <c r="E2" s="65" t="inlineStr">
         <is>
           <t>Precision</t>
         </is>
       </c>
-      <c r="F2" s="18" t="inlineStr">
+      <c r="F2" s="65" t="inlineStr">
         <is>
           <t>Recall</t>
         </is>
       </c>
-      <c r="G2" s="18" t="inlineStr">
+      <c r="G2" s="65" t="inlineStr">
         <is>
           <t>F1 Score</t>
         </is>
       </c>
-      <c r="H2" s="18" t="inlineStr">
+      <c r="H2" s="65" t="inlineStr">
         <is>
           <t>Last Trained</t>
         </is>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="29" t="inlineStr">
+      <c r="A3" s="64" t="inlineStr">
         <is>
           <t>Probability of Default (PD)</t>
         </is>
       </c>
-      <c r="B3" s="42" t="inlineStr">
+      <c r="B3" s="63" t="inlineStr">
         <is>
           <t>XGBoost</t>
         </is>
       </c>
-      <c r="C3" s="43" t="n">
+      <c r="C3" s="78" t="n">
         <v>28000</v>
       </c>
       <c r="D3" s="44" t="n">
         <v>0.847</v>
       </c>
-      <c r="E3" s="45" t="n">
+      <c r="E3" s="79" t="n">
         <v>0.781</v>
       </c>
-      <c r="F3" s="45" t="n">
+      <c r="F3" s="79" t="n">
         <v>0.823</v>
       </c>
-      <c r="G3" s="45">
+      <c r="G3" s="79">
         <f>2*E3*F3/(E3+F3)</f>
         <v/>
       </c>
-      <c r="H3" s="46" t="inlineStr">
+      <c r="H3" s="62" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
@@ -2251,33 +2385,33 @@
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="64" t="inlineStr">
         <is>
           <t>Fraud Ensemble</t>
         </is>
       </c>
-      <c r="B5" s="42" t="inlineStr">
+      <c r="B5" s="63" t="inlineStr">
         <is>
           <t>Random Forest + XGBoost</t>
         </is>
       </c>
-      <c r="C5" s="43" t="n">
+      <c r="C5" s="78" t="n">
         <v>199600</v>
       </c>
       <c r="D5" s="51" t="n">
         <v>0.963</v>
       </c>
-      <c r="E5" s="45" t="n">
+      <c r="E5" s="79" t="n">
         <v>0.887</v>
       </c>
-      <c r="F5" s="45" t="n">
+      <c r="F5" s="79" t="n">
         <v>0.912</v>
       </c>
-      <c r="G5" s="45">
+      <c r="G5" s="79">
         <f>2*E5*F5/(E5+F5)</f>
         <v/>
       </c>
-      <c r="H5" s="46" t="inlineStr">
+      <c r="H5" s="62" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
@@ -2323,6 +2457,13 @@
           <t>PERFORMANCE THRESHOLDS</t>
         </is>
       </c>
+      <c r="B8" s="52" t="n"/>
+      <c r="C8" s="52" t="n"/>
+      <c r="D8" s="52" t="n"/>
+      <c r="E8" s="52" t="n"/>
+      <c r="F8" s="52" t="n"/>
+      <c r="G8" s="52" t="n"/>
+      <c r="H8" s="53" t="n"/>
     </row>
     <row r="9" ht="16" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
@@ -2362,6 +2503,11 @@
           <t>Production-ready — quarterly review cycle</t>
         </is>
       </c>
+      <c r="D10" s="52" t="n"/>
+      <c r="E10" s="52" t="n"/>
+      <c r="F10" s="52" t="n"/>
+      <c r="G10" s="52" t="n"/>
+      <c r="H10" s="53" t="n"/>
     </row>
     <row r="11" ht="16" customHeight="1">
       <c r="A11" s="57" t="inlineStr">
@@ -2379,6 +2525,11 @@
           <t>Acceptable — monthly monitoring</t>
         </is>
       </c>
+      <c r="D11" s="52" t="n"/>
+      <c r="E11" s="52" t="n"/>
+      <c r="F11" s="52" t="n"/>
+      <c r="G11" s="52" t="n"/>
+      <c r="H11" s="53" t="n"/>
     </row>
     <row r="12" ht="16" customHeight="1">
       <c r="A12" s="58" t="inlineStr">
@@ -2396,6 +2547,11 @@
           <t>Needs improvement — weekly review</t>
         </is>
       </c>
+      <c r="D12" s="52" t="n"/>
+      <c r="E12" s="52" t="n"/>
+      <c r="F12" s="52" t="n"/>
+      <c r="G12" s="52" t="n"/>
+      <c r="H12" s="53" t="n"/>
     </row>
     <row r="13" ht="16" customHeight="1">
       <c r="A13" s="59" t="inlineStr">
@@ -2413,6 +2569,11 @@
           <t>Requires retraining or replacement</t>
         </is>
       </c>
+      <c r="D13" s="52" t="n"/>
+      <c r="E13" s="52" t="n"/>
+      <c r="F13" s="52" t="n"/>
+      <c r="G13" s="52" t="n"/>
+      <c r="H13" s="53" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
